--- a/tools/importer/reports/import-dxs-service-and-supports.report.xlsx
+++ b/tools/importer/reports/import-dxs-service-and-supports.report.xlsx
@@ -73,7 +73,7 @@
     <t>solutions</t>
   </si>
   <si>
-    <t>2026-10-21T13:18:34.822Z</t>
+    <t>2026-10-22T07:38:20.845Z</t>
   </si>
   <si>
     <t>Host Response Infection | Beckman Coulter</t>
@@ -94,7 +94,7 @@
     <t>dxs-service-and-supports</t>
   </si>
   <si>
-    <t>2026-10-22T07:10:09.012Z</t>
+    <t>2026-10-22T07:38:30.844Z</t>
   </si>
   <si>
     <t>Remote Services and Diagnostics | Beckman Coulter</t>
